--- a/data/raw/sales/Week 11/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 11/Audio_Array/other_channels.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="D5" s="21" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E5" s="25" t="n">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>AH-45-BK</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -7299,7 +7299,7 @@
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>FBA79977</t>
+          <t>FBA80006</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>BM-320 PRO</t>
+          <t>A2-XLR</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
